--- a/artfynd/S 2274-2026 artfynd.xlsx
+++ b/artfynd/S 2274-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194232</v>
       </c>
       <c r="B2" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194231</v>
       </c>
       <c r="B3" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
